--- a/policyengine_uk/tests/fixtures/obr_receipts/obr_efo_october_2026_receipts.xlsx
+++ b/policyengine_uk/tests/fixtures/obr_receipts/obr_efo_october_2026_receipts.xlsx
@@ -18,6 +18,7 @@
     <ns0:sheet name="4.2" sheetId="263" ns7:id="rId4"/>
     <ns0:sheet name="4.7" sheetId="204" ns7:id="rId9"/>
     <ns0:sheet name="4.8" sheetId="192" ns7:id="rId10"/>
+    <ns0:sheet name="4.10" sheetId="261" ns7:id="rId12"/>
   </ns0:sheets>
   <ns0:definedNames>
     <ns0:definedName name="________tab3" localSheetId="19">!#REF!</ns0:definedName>
@@ -7702,6 +7703,644 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{270C67AD-4C14-4065-AB23-9509227752CC}">
+  <sheetPr>
+    <tabColor theme="6"/>
+  </sheetPr>
+  <dimension ref="A1:V41"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5"/>
+  <cols>
+    <col min="1" max="1" width="11.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" style="1" customWidth="1"/>
+    <col min="3" max="8" width="10" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.1796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" s="317" customFormat="1" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A1" s="318" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22" s="317" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="B2" s="945" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="946"/>
+      <c r="D2" s="946"/>
+      <c r="E2" s="946"/>
+      <c r="F2" s="946"/>
+      <c r="G2" s="946"/>
+      <c r="H2" s="947"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+    </row>
+    <row r="3" spans="1:22" s="317" customFormat="1" ht="12.75" customHeight="1">
+      <c r="B3" s="322"/>
+      <c r="C3" s="941" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="941"/>
+      <c r="E3" s="941"/>
+      <c r="F3" s="941"/>
+      <c r="G3" s="941"/>
+      <c r="H3" s="942"/>
+      <c r="J3" s="755"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="756"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+    </row>
+    <row r="4" spans="1:22" s="317" customFormat="1" ht="12.75" customHeight="1">
+      <c r="B4" s="261"/>
+      <c r="C4" s="939" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="939"/>
+      <c r="E4" s="939"/>
+      <c r="F4" s="939"/>
+      <c r="G4" s="939"/>
+      <c r="H4" s="940"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+    </row>
+    <row r="5" spans="1:22" s="317" customFormat="1" ht="12.75" customHeight="1">
+      <c r="B5" s="261"/>
+      <c r="C5" s="258" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="258" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="258" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="258" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" s="258" t="s">
+        <v>201</v>
+      </c>
+      <c r="H5" s="319" t="s">
+        <v>267</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+    </row>
+    <row r="6" spans="1:22" s="317" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B6" s="262" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="329">
+        <v>5.0924733650374945</v>
+      </c>
+      <c r="D6" s="329">
+        <v>5.5228648933437334</v>
+      </c>
+      <c r="E6" s="329">
+        <v>5.6794261593536906</v>
+      </c>
+      <c r="F6" s="329">
+        <v>5.8110692066966134</v>
+      </c>
+      <c r="G6" s="329">
+        <v>5.9157448460764925</v>
+      </c>
+      <c r="H6" s="330">
+        <v>6.0093468668139112</v>
+      </c>
+      <c r="J6" s="757"/>
+      <c r="K6" s="757"/>
+      <c r="L6" s="757"/>
+      <c r="M6" s="757"/>
+      <c r="N6" s="757"/>
+      <c r="O6" s="757"/>
+      <c r="P6" s="758"/>
+      <c r="Q6" s="759"/>
+      <c r="R6" s="759"/>
+      <c r="S6" s="759"/>
+      <c r="T6" s="759"/>
+      <c r="U6" s="759"/>
+      <c r="V6" s="759"/>
+    </row>
+    <row r="7" spans="1:22" s="317" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B7" s="263" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="259"/>
+      <c r="D7" s="259"/>
+      <c r="E7" s="259"/>
+      <c r="F7" s="259"/>
+      <c r="G7" s="259"/>
+      <c r="H7" s="260"/>
+      <c r="J7" s="757"/>
+      <c r="K7" s="757"/>
+      <c r="L7" s="757"/>
+      <c r="M7" s="757"/>
+      <c r="N7" s="757"/>
+      <c r="O7" s="757"/>
+      <c r="P7" s="758"/>
+      <c r="Q7" s="759"/>
+      <c r="R7" s="759"/>
+      <c r="S7" s="759"/>
+      <c r="T7" s="759"/>
+      <c r="U7" s="759"/>
+      <c r="V7" s="759"/>
+    </row>
+    <row r="8" spans="1:22" s="317" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B8" s="264" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="259">
+        <v>2.7520296250837784</v>
+      </c>
+      <c r="D8" s="259">
+        <v>2.7812750734699425</v>
+      </c>
+      <c r="E8" s="259">
+        <v>2.8416867878041874</v>
+      </c>
+      <c r="F8" s="259">
+        <v>2.9053716896455919</v>
+      </c>
+      <c r="G8" s="259">
+        <v>2.9446821891345443</v>
+      </c>
+      <c r="H8" s="260">
+        <v>2.963204761653297</v>
+      </c>
+      <c r="J8" s="757"/>
+      <c r="K8" s="757"/>
+      <c r="L8" s="757"/>
+      <c r="M8" s="757"/>
+      <c r="N8" s="757"/>
+      <c r="O8" s="757"/>
+      <c r="P8" s="758"/>
+      <c r="Q8" s="759"/>
+      <c r="R8" s="759"/>
+      <c r="S8" s="759"/>
+      <c r="T8" s="759"/>
+      <c r="U8" s="759"/>
+      <c r="V8" s="759"/>
+    </row>
+    <row r="9" spans="1:22" s="317" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B9" s="264" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="259">
+        <v>0.83052038459597621</v>
+      </c>
+      <c r="D9" s="259">
+        <v>0.84965566898040046</v>
+      </c>
+      <c r="E9" s="259">
+        <v>0.87574553838772884</v>
+      </c>
+      <c r="F9" s="259">
+        <v>0.90350845044750805</v>
+      </c>
+      <c r="G9" s="259">
+        <v>0.92958587301870155</v>
+      </c>
+      <c r="H9" s="260">
+        <v>0.95685079671453654</v>
+      </c>
+      <c r="J9" s="757"/>
+      <c r="K9" s="757"/>
+      <c r="L9" s="757"/>
+      <c r="M9" s="757"/>
+      <c r="N9" s="757"/>
+      <c r="O9" s="757"/>
+      <c r="P9" s="758"/>
+      <c r="Q9" s="759"/>
+      <c r="R9" s="759"/>
+      <c r="S9" s="759"/>
+      <c r="T9" s="759"/>
+      <c r="U9" s="759"/>
+      <c r="V9" s="759"/>
+    </row>
+    <row r="10" spans="1:22" s="317" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B10" s="264" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="259">
+        <v>0.65560522982822456</v>
+      </c>
+      <c r="D10" s="259">
+        <v>0.87744453968275893</v>
+      </c>
+      <c r="E10" s="259">
+        <v>0.91694664204685206</v>
+      </c>
+      <c r="F10" s="259">
+        <v>0.94862995017184315</v>
+      </c>
+      <c r="G10" s="259">
+        <v>0.97646741817020943</v>
+      </c>
+      <c r="H10" s="260">
+        <v>1.0041740187990271</v>
+      </c>
+      <c r="J10" s="757"/>
+      <c r="K10" s="757"/>
+      <c r="L10" s="757"/>
+      <c r="M10" s="757"/>
+      <c r="N10" s="757"/>
+      <c r="O10" s="757"/>
+      <c r="P10" s="758"/>
+      <c r="Q10" s="759"/>
+      <c r="R10" s="759"/>
+      <c r="S10" s="759"/>
+      <c r="T10" s="759"/>
+      <c r="U10" s="759"/>
+      <c r="V10" s="759"/>
+    </row>
+    <row r="11" spans="1:22" s="317" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B11" s="264" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="259">
+        <v>0.67707068705786499</v>
+      </c>
+      <c r="D11" s="259">
+        <v>0.82692873727074745</v>
+      </c>
+      <c r="E11" s="259">
+        <v>0.85695449075649544</v>
+      </c>
+      <c r="F11" s="259">
+        <v>0.86524127517297356</v>
+      </c>
+      <c r="G11" s="259">
+        <v>0.87550370868921701</v>
+      </c>
+      <c r="H11" s="260">
+        <v>0.89631020781238802</v>
+      </c>
+      <c r="J11" s="757"/>
+      <c r="K11" s="757"/>
+      <c r="L11" s="757"/>
+      <c r="M11" s="757"/>
+      <c r="N11" s="757"/>
+      <c r="O11" s="757"/>
+      <c r="P11" s="758"/>
+      <c r="Q11" s="759"/>
+      <c r="R11" s="759"/>
+      <c r="S11" s="759"/>
+      <c r="T11" s="759"/>
+      <c r="U11" s="759"/>
+      <c r="V11" s="759"/>
+    </row>
+    <row r="12" spans="1:22" s="317" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B12" s="264" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="259">
+        <v>0.17422987982556123</v>
+      </c>
+      <c r="D12" s="259">
+        <v>0.18488058456996015</v>
+      </c>
+      <c r="E12" s="259">
+        <v>0.18523427331264838</v>
+      </c>
+      <c r="F12" s="259">
+        <v>0.18548069649974164</v>
+      </c>
+      <c r="G12" s="259">
+        <v>0.18650974968911124</v>
+      </c>
+      <c r="H12" s="260">
+        <v>0.18568125218312026</v>
+      </c>
+      <c r="J12" s="757"/>
+      <c r="K12" s="757"/>
+      <c r="L12" s="757"/>
+      <c r="M12" s="757"/>
+      <c r="N12" s="757"/>
+      <c r="O12" s="757"/>
+      <c r="P12" s="758"/>
+      <c r="Q12" s="759"/>
+      <c r="R12" s="759"/>
+      <c r="S12" s="759"/>
+      <c r="T12" s="759"/>
+      <c r="U12" s="759"/>
+      <c r="V12" s="759"/>
+    </row>
+    <row r="13" spans="1:22" s="317" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B13" s="264" t="s">
+        <v>226</v>
+      </c>
+      <c r="C13" s="259">
+        <v>1.8867652000000002E-4</v>
+      </c>
+      <c r="D13" s="259">
+        <v>0</v>
+      </c>
+      <c r="E13" s="259">
+        <v>0</v>
+      </c>
+      <c r="F13" s="259">
+        <v>0</v>
+      </c>
+      <c r="G13" s="259">
+        <v>0</v>
+      </c>
+      <c r="H13" s="260">
+        <v>0</v>
+      </c>
+      <c r="J13" s="757"/>
+      <c r="K13" s="757"/>
+      <c r="L13" s="757"/>
+      <c r="M13" s="757"/>
+      <c r="N13" s="757"/>
+      <c r="O13" s="757"/>
+      <c r="P13" s="758"/>
+      <c r="Q13" s="759"/>
+      <c r="R13" s="759"/>
+      <c r="S13" s="759"/>
+      <c r="T13" s="759"/>
+      <c r="U13" s="759"/>
+      <c r="V13" s="759"/>
+    </row>
+    <row r="14" spans="1:22" s="317" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B14" s="265" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="320">
+        <v>2.8288821260900035E-3</v>
+      </c>
+      <c r="D14" s="320">
+        <v>2.6802893699237468E-3</v>
+      </c>
+      <c r="E14" s="320">
+        <v>2.85842704577818E-3</v>
+      </c>
+      <c r="F14" s="320">
+        <v>2.8371447589557743E-3</v>
+      </c>
+      <c r="G14" s="320">
+        <v>2.9959073747097458E-3</v>
+      </c>
+      <c r="H14" s="321">
+        <v>3.1258296515431082E-3</v>
+      </c>
+      <c r="J14" s="757"/>
+      <c r="K14" s="757"/>
+      <c r="L14" s="757"/>
+      <c r="M14" s="757"/>
+      <c r="N14" s="757"/>
+      <c r="O14" s="757"/>
+      <c r="P14" s="758"/>
+      <c r="Q14" s="759"/>
+      <c r="R14" s="759"/>
+      <c r="S14" s="759"/>
+      <c r="T14" s="759"/>
+      <c r="U14" s="759"/>
+      <c r="V14" s="759"/>
+    </row>
+    <row r="15" spans="1:22" s="317" customFormat="1">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+    </row>
+    <row r="18" spans="2:8" ht="18.5">
+      <c r="B18" s="948"/>
+      <c r="C18" s="948"/>
+      <c r="D18" s="948"/>
+      <c r="E18" s="948"/>
+      <c r="F18" s="948"/>
+      <c r="G18" s="948"/>
+      <c r="H18" s="948"/>
+    </row>
+    <row r="19" spans="2:8" ht="13">
+      <c r="B19" s="124"/>
+      <c r="C19" s="944"/>
+      <c r="D19" s="944"/>
+      <c r="E19" s="944"/>
+      <c r="F19" s="944"/>
+      <c r="G19" s="944"/>
+      <c r="H19" s="944"/>
+    </row>
+    <row r="20" spans="2:8" ht="13">
+      <c r="B20" s="124"/>
+      <c r="C20" s="943"/>
+      <c r="D20" s="943"/>
+      <c r="E20" s="943"/>
+      <c r="F20" s="943"/>
+      <c r="G20" s="943"/>
+      <c r="H20" s="943"/>
+    </row>
+    <row r="21" spans="2:8" ht="13">
+      <c r="B21" s="124"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="124"/>
+      <c r="G21" s="124"/>
+      <c r="H21" s="124"/>
+    </row>
+    <row r="22" spans="2:8" ht="13">
+      <c r="B22" s="752"/>
+      <c r="C22" s="431"/>
+      <c r="D22" s="431"/>
+      <c r="E22" s="431"/>
+      <c r="F22" s="431"/>
+      <c r="G22" s="431"/>
+      <c r="H22" s="431"/>
+    </row>
+    <row r="23" spans="2:8" ht="13">
+      <c r="B23" s="753"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+    </row>
+    <row r="24" spans="2:8" ht="13">
+      <c r="B24" s="754"/>
+      <c r="C24" s="435"/>
+      <c r="D24" s="435"/>
+      <c r="E24" s="435"/>
+      <c r="F24" s="435"/>
+      <c r="G24" s="435"/>
+      <c r="H24" s="435"/>
+    </row>
+    <row r="25" spans="2:8" ht="13">
+      <c r="B25" s="754"/>
+      <c r="C25" s="435"/>
+      <c r="D25" s="435"/>
+      <c r="E25" s="435"/>
+      <c r="F25" s="435"/>
+      <c r="G25" s="435"/>
+      <c r="H25" s="435"/>
+    </row>
+    <row r="26" spans="2:8" ht="13">
+      <c r="B26" s="754"/>
+      <c r="C26" s="435"/>
+      <c r="D26" s="435"/>
+      <c r="E26" s="435"/>
+      <c r="F26" s="435"/>
+      <c r="G26" s="435"/>
+      <c r="H26" s="435"/>
+    </row>
+    <row r="27" spans="2:8" ht="13">
+      <c r="B27" s="754"/>
+      <c r="C27" s="435"/>
+      <c r="D27" s="435"/>
+      <c r="E27" s="435"/>
+      <c r="F27" s="435"/>
+      <c r="G27" s="435"/>
+      <c r="H27" s="435"/>
+    </row>
+    <row r="28" spans="2:8" ht="13">
+      <c r="B28" s="754"/>
+      <c r="C28" s="435"/>
+      <c r="D28" s="435"/>
+      <c r="E28" s="435"/>
+      <c r="F28" s="435"/>
+      <c r="G28" s="435"/>
+      <c r="H28" s="435"/>
+    </row>
+    <row r="29" spans="2:8" ht="13">
+      <c r="B29" s="754"/>
+      <c r="C29" s="435"/>
+      <c r="D29" s="435"/>
+      <c r="E29" s="435"/>
+      <c r="F29" s="435"/>
+      <c r="G29" s="435"/>
+      <c r="H29" s="435"/>
+    </row>
+    <row r="30" spans="2:8" ht="13">
+      <c r="B30" s="754"/>
+      <c r="C30" s="435"/>
+      <c r="D30" s="435"/>
+      <c r="E30" s="435"/>
+      <c r="F30" s="435"/>
+      <c r="G30" s="435"/>
+      <c r="H30" s="435"/>
+    </row>
+    <row r="34" spans="2:8" s="587" customFormat="1" ht="13">
+      <c r="B34" s="761"/>
+      <c r="C34" s="184"/>
+      <c r="D34" s="184"/>
+      <c r="E34" s="184"/>
+      <c r="F34" s="184"/>
+      <c r="G34" s="184"/>
+      <c r="H34" s="184"/>
+    </row>
+    <row r="35" spans="2:8" s="587" customFormat="1">
+      <c r="B35" s="184"/>
+      <c r="C35" s="762"/>
+      <c r="D35" s="762"/>
+      <c r="E35" s="762"/>
+      <c r="F35" s="762"/>
+      <c r="G35" s="762"/>
+      <c r="H35" s="762"/>
+    </row>
+    <row r="36" spans="2:8" s="587" customFormat="1">
+      <c r="B36" s="184"/>
+      <c r="C36" s="762"/>
+      <c r="D36" s="762"/>
+      <c r="E36" s="762"/>
+      <c r="F36" s="762"/>
+      <c r="G36" s="762"/>
+      <c r="H36" s="762"/>
+    </row>
+    <row r="37" spans="2:8" s="587" customFormat="1">
+      <c r="B37" s="184"/>
+      <c r="C37" s="762"/>
+      <c r="D37" s="762"/>
+      <c r="E37" s="762"/>
+      <c r="F37" s="762"/>
+      <c r="G37" s="762"/>
+      <c r="H37" s="762"/>
+    </row>
+    <row r="38" spans="2:8" s="587" customFormat="1"/>
+    <row r="39" spans="2:8" s="587" customFormat="1"/>
+    <row r="40" spans="2:8" s="587" customFormat="1"/>
+    <row r="41" spans="2:8" s="587" customFormat="1"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B18:H18"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Contents!A1" display="Back to contents" xr:uid="{8326E600-4ACE-4B09-A201-6586B1299CBB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C832A33-B09A-486C-90AD-7C64006FA8C9}">
   <sheetPr codeName="Sheet25">

--- a/policyengine_uk/tests/fixtures/obr_receipts/obr_efo_october_2026_receipts.xlsx
+++ b/policyengine_uk/tests/fixtures/obr_receipts/obr_efo_october_2026_receipts.xlsx
@@ -19,6 +19,8 @@
     <ns0:sheet name="4.7" sheetId="204" ns7:id="rId9"/>
     <ns0:sheet name="4.8" sheetId="192" ns7:id="rId10"/>
     <ns0:sheet name="4.10" sheetId="261" ns7:id="rId12"/>
+    <ns0:sheet name="4.11" sheetId="208" ns7:id="rId13"/>
+    <ns0:sheet name="4.12" sheetId="209" ns7:id="rId14"/>
   </ns0:sheets>
   <ns0:definedNames>
     <ns0:definedName name="________tab3" localSheetId="19">!#REF!</ns0:definedName>
@@ -8341,6 +8343,1430 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD633EC-985A-453A-B0BD-4801B0D465F1}">
+  <sheetPr codeName="Sheet13">
+    <tabColor theme="6"/>
+  </sheetPr>
+  <dimension ref="A1:T35"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="11.7265625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" style="17" customWidth="1"/>
+    <col min="3" max="9" width="10" style="17" customWidth="1"/>
+    <col min="10" max="16384" width="9.453125" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" s="15" customFormat="1" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="139"/>
+      <c r="K1" s="526"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+    </row>
+    <row r="2" spans="1:20" s="15" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="B2" s="916" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2" s="917"/>
+      <c r="D2" s="917"/>
+      <c r="E2" s="917"/>
+      <c r="F2" s="917"/>
+      <c r="G2" s="917"/>
+      <c r="H2" s="917"/>
+      <c r="I2" s="918"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+    </row>
+    <row r="3" spans="1:20" s="15" customFormat="1" ht="12.75" customHeight="1">
+      <c r="B3" s="140"/>
+      <c r="C3" s="105" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="949" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="949"/>
+      <c r="F3" s="949"/>
+      <c r="G3" s="949"/>
+      <c r="H3" s="949"/>
+      <c r="I3" s="950"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="559"/>
+      <c r="M3" s="559"/>
+      <c r="N3" s="559"/>
+      <c r="O3" s="559"/>
+      <c r="P3" s="559"/>
+      <c r="Q3" s="559"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+    </row>
+    <row r="4" spans="1:20" s="15" customFormat="1" ht="12.75" customHeight="1">
+      <c r="B4" s="141"/>
+      <c r="C4" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="K4" s="532"/>
+      <c r="L4" s="532"/>
+      <c r="M4" s="532"/>
+      <c r="N4" s="532"/>
+      <c r="O4" s="532"/>
+      <c r="P4" s="532"/>
+      <c r="Q4" s="532"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+    </row>
+    <row r="5" spans="1:20" s="15" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B5" s="142" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="143">
+        <v>12224.568453264392</v>
+      </c>
+      <c r="D5" s="143">
+        <v>10962.756413840059</v>
+      </c>
+      <c r="E5" s="143">
+        <v>9853.5452739735829</v>
+      </c>
+      <c r="F5" s="143">
+        <v>9042.8621730867635</v>
+      </c>
+      <c r="G5" s="143">
+        <v>8222.5673694138313</v>
+      </c>
+      <c r="H5" s="143">
+        <v>7677.1786518547042</v>
+      </c>
+      <c r="I5" s="144">
+        <v>7165.065963684312</v>
+      </c>
+      <c r="K5" s="630"/>
+      <c r="L5" s="630"/>
+      <c r="M5" s="630"/>
+      <c r="N5" s="630"/>
+      <c r="O5" s="630"/>
+      <c r="P5" s="630"/>
+      <c r="Q5" s="630"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+    </row>
+    <row r="6" spans="1:20" s="15" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B6" s="145" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="143">
+        <v>3939.7419080850214</v>
+      </c>
+      <c r="D6" s="143">
+        <v>3683.461884582161</v>
+      </c>
+      <c r="E6" s="143">
+        <v>3434.3137168974845</v>
+      </c>
+      <c r="F6" s="143">
+        <v>3151.6683337066188</v>
+      </c>
+      <c r="G6" s="143">
+        <v>2960.2573475405547</v>
+      </c>
+      <c r="H6" s="143">
+        <v>2845.1580105682265</v>
+      </c>
+      <c r="I6" s="144">
+        <v>2708.24460555327</v>
+      </c>
+      <c r="K6" s="630"/>
+      <c r="L6" s="630"/>
+      <c r="M6" s="630"/>
+      <c r="N6" s="630"/>
+      <c r="O6" s="630"/>
+      <c r="P6" s="630"/>
+      <c r="Q6" s="630"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+    </row>
+    <row r="7" spans="1:20" s="15" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B7" s="309" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="143"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="143"/>
+      <c r="F7" s="143"/>
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
+      <c r="I7" s="144"/>
+      <c r="K7" s="630"/>
+      <c r="L7" s="630"/>
+      <c r="M7" s="630"/>
+      <c r="N7" s="630"/>
+      <c r="O7" s="630"/>
+      <c r="P7" s="630"/>
+      <c r="Q7" s="630"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+    </row>
+    <row r="8" spans="1:20" s="15" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B8" s="146" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="143">
+        <v>3338.0207129187247</v>
+      </c>
+      <c r="D8" s="143">
+        <v>3112.6781722236924</v>
+      </c>
+      <c r="E8" s="143">
+        <v>2886.8250342433803</v>
+      </c>
+      <c r="F8" s="143">
+        <v>2649.2381871262742</v>
+      </c>
+      <c r="G8" s="143">
+        <v>2482.242556381048</v>
+      </c>
+      <c r="H8" s="143">
+        <v>2384.6513795861088</v>
+      </c>
+      <c r="I8" s="144">
+        <v>2273.4315215751089</v>
+      </c>
+      <c r="K8" s="630"/>
+      <c r="L8" s="630"/>
+      <c r="M8" s="630"/>
+      <c r="N8" s="630"/>
+      <c r="O8" s="630"/>
+      <c r="P8" s="630"/>
+      <c r="Q8" s="630"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+    </row>
+    <row r="9" spans="1:20" s="15" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B9" s="147" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="148">
+        <v>601.72119516629675</v>
+      </c>
+      <c r="D9" s="148">
+        <v>570.78371235846851</v>
+      </c>
+      <c r="E9" s="148">
+        <v>547.48868265410397</v>
+      </c>
+      <c r="F9" s="148">
+        <v>502.43014658034485</v>
+      </c>
+      <c r="G9" s="148">
+        <v>478.01479115950667</v>
+      </c>
+      <c r="H9" s="148">
+        <v>460.50663098211788</v>
+      </c>
+      <c r="I9" s="149">
+        <v>434.81308397816122</v>
+      </c>
+      <c r="K9" s="630"/>
+      <c r="L9" s="630"/>
+      <c r="M9" s="630"/>
+      <c r="N9" s="630"/>
+      <c r="O9" s="630"/>
+      <c r="P9" s="630"/>
+      <c r="Q9" s="630"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+    </row>
+    <row r="10" spans="1:20" s="15" customFormat="1">
+      <c r="B10" s="64"/>
+      <c r="C10" s="143"/>
+      <c r="D10" s="143"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+    </row>
+    <row r="11" spans="1:20" s="15" customFormat="1" ht="13.5" customHeight="1">
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="B12" s="536"/>
+    </row>
+    <row r="13" spans="1:20" ht="18.5">
+      <c r="B13" s="951"/>
+      <c r="C13" s="951"/>
+      <c r="D13" s="951"/>
+      <c r="E13" s="951"/>
+      <c r="F13" s="951"/>
+      <c r="G13" s="951"/>
+      <c r="H13" s="951"/>
+      <c r="I13" s="951"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="B14" s="633"/>
+      <c r="C14" s="531"/>
+      <c r="D14" s="952"/>
+      <c r="E14" s="952"/>
+      <c r="F14" s="952"/>
+      <c r="G14" s="952"/>
+      <c r="H14" s="952"/>
+      <c r="I14" s="952"/>
+      <c r="K14" s="568"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="B15" s="634"/>
+      <c r="C15" s="532"/>
+      <c r="D15" s="532"/>
+      <c r="E15" s="532"/>
+      <c r="F15" s="532"/>
+      <c r="G15" s="532"/>
+      <c r="H15" s="532"/>
+      <c r="I15" s="532"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="B16" s="635"/>
+      <c r="C16" s="629"/>
+      <c r="D16" s="629"/>
+      <c r="E16" s="629"/>
+      <c r="F16" s="629"/>
+      <c r="G16" s="629"/>
+      <c r="H16" s="629"/>
+      <c r="I16" s="629"/>
+      <c r="M16" s="631"/>
+      <c r="N16" s="631"/>
+      <c r="O16" s="631"/>
+      <c r="P16" s="631"/>
+      <c r="Q16" s="631"/>
+    </row>
+    <row r="17" spans="2:20">
+      <c r="B17" s="636"/>
+      <c r="C17" s="629"/>
+      <c r="D17" s="629"/>
+      <c r="E17" s="629"/>
+      <c r="F17" s="629"/>
+      <c r="G17" s="629"/>
+      <c r="H17" s="629"/>
+      <c r="I17" s="629"/>
+    </row>
+    <row r="18" spans="2:20">
+      <c r="B18" s="637"/>
+      <c r="C18" s="629"/>
+      <c r="D18" s="629"/>
+      <c r="E18" s="629"/>
+      <c r="F18" s="629"/>
+      <c r="G18" s="629"/>
+      <c r="H18" s="629"/>
+      <c r="I18" s="629"/>
+    </row>
+    <row r="19" spans="2:20">
+      <c r="B19" s="638"/>
+      <c r="C19" s="629"/>
+      <c r="D19" s="629"/>
+      <c r="E19" s="629"/>
+      <c r="F19" s="629"/>
+      <c r="G19" s="629"/>
+      <c r="H19" s="629"/>
+      <c r="I19" s="629"/>
+    </row>
+    <row r="20" spans="2:20">
+      <c r="B20" s="64"/>
+      <c r="C20" s="629"/>
+      <c r="D20" s="629"/>
+      <c r="E20" s="629"/>
+      <c r="F20" s="629"/>
+      <c r="G20" s="629"/>
+      <c r="H20" s="629"/>
+      <c r="I20" s="629"/>
+    </row>
+    <row r="21" spans="2:20" s="15" customFormat="1">
+      <c r="B21" s="64"/>
+      <c r="C21" s="143"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="143"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
+      <c r="I21" s="143"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+    </row>
+    <row r="22" spans="2:20" s="15" customFormat="1">
+      <c r="B22" s="64"/>
+      <c r="C22" s="143"/>
+      <c r="D22" s="143"/>
+      <c r="E22" s="143"/>
+      <c r="F22" s="143"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="143"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+    </row>
+    <row r="23" spans="2:20">
+      <c r="B23" s="64"/>
+      <c r="C23" s="629"/>
+      <c r="D23" s="629"/>
+      <c r="E23" s="629"/>
+      <c r="F23" s="629"/>
+      <c r="G23" s="629"/>
+      <c r="H23" s="629"/>
+      <c r="I23" s="629"/>
+    </row>
+    <row r="24" spans="2:20">
+      <c r="B24" s="64"/>
+      <c r="C24" s="629"/>
+      <c r="D24" s="629"/>
+      <c r="E24" s="629"/>
+      <c r="F24" s="629"/>
+      <c r="G24" s="629"/>
+      <c r="H24" s="629"/>
+      <c r="I24" s="629"/>
+    </row>
+    <row r="25" spans="2:20">
+      <c r="C25" s="629"/>
+      <c r="D25" s="629"/>
+      <c r="E25" s="629"/>
+      <c r="F25" s="629"/>
+      <c r="G25" s="629"/>
+      <c r="H25" s="629"/>
+      <c r="I25" s="629"/>
+    </row>
+    <row r="26" spans="2:20">
+      <c r="C26" s="629"/>
+      <c r="D26" s="629"/>
+      <c r="E26" s="629"/>
+      <c r="F26" s="629"/>
+      <c r="G26" s="629"/>
+      <c r="H26" s="629"/>
+      <c r="I26" s="629"/>
+    </row>
+    <row r="27" spans="2:20">
+      <c r="C27" s="629"/>
+      <c r="D27" s="629"/>
+      <c r="E27" s="629"/>
+      <c r="F27" s="629"/>
+      <c r="G27" s="629"/>
+      <c r="H27" s="629"/>
+      <c r="I27" s="629"/>
+    </row>
+    <row r="28" spans="2:20">
+      <c r="C28" s="629"/>
+      <c r="D28" s="629"/>
+      <c r="E28" s="629"/>
+      <c r="F28" s="629"/>
+      <c r="G28" s="629"/>
+      <c r="H28" s="629"/>
+      <c r="I28" s="629"/>
+    </row>
+    <row r="29" spans="2:20">
+      <c r="B29" s="86"/>
+      <c r="C29" s="620"/>
+      <c r="D29" s="536"/>
+      <c r="E29" s="536"/>
+      <c r="F29" s="536"/>
+      <c r="G29" s="536"/>
+      <c r="H29" s="536"/>
+      <c r="I29" s="536"/>
+      <c r="J29" s="536"/>
+    </row>
+    <row r="30" spans="2:20">
+      <c r="B30" s="536"/>
+      <c r="C30" s="536"/>
+      <c r="D30" s="536"/>
+      <c r="E30" s="536"/>
+      <c r="F30" s="536"/>
+      <c r="G30" s="536"/>
+      <c r="H30" s="536"/>
+      <c r="I30" s="536"/>
+      <c r="J30" s="536"/>
+    </row>
+    <row r="31" spans="2:20">
+      <c r="B31" s="536"/>
+      <c r="C31" s="630"/>
+      <c r="D31" s="630"/>
+      <c r="E31" s="630"/>
+      <c r="F31" s="630"/>
+      <c r="G31" s="630"/>
+      <c r="H31" s="630"/>
+      <c r="I31" s="630"/>
+      <c r="J31" s="536"/>
+    </row>
+    <row r="32" spans="2:20">
+      <c r="B32" s="536"/>
+      <c r="C32" s="630"/>
+      <c r="D32" s="630"/>
+      <c r="E32" s="630"/>
+      <c r="F32" s="630"/>
+      <c r="G32" s="630"/>
+      <c r="H32" s="630"/>
+      <c r="I32" s="630"/>
+      <c r="J32" s="536"/>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" s="536"/>
+      <c r="C33" s="630"/>
+      <c r="D33" s="630"/>
+      <c r="E33" s="630"/>
+      <c r="F33" s="630"/>
+      <c r="G33" s="630"/>
+      <c r="H33" s="630"/>
+      <c r="I33" s="630"/>
+      <c r="J33" s="536"/>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="B34" s="536"/>
+      <c r="C34" s="536"/>
+      <c r="D34" s="536"/>
+      <c r="E34" s="536"/>
+      <c r="F34" s="536"/>
+      <c r="G34" s="536"/>
+      <c r="H34" s="536"/>
+      <c r="I34" s="536"/>
+      <c r="J34" s="536"/>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35" s="536"/>
+      <c r="C35" s="536"/>
+      <c r="D35" s="536"/>
+      <c r="E35" s="536"/>
+      <c r="F35" s="536"/>
+      <c r="G35" s="536"/>
+      <c r="H35" s="536"/>
+      <c r="I35" s="536"/>
+      <c r="J35" s="536"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="D14:I14"/>
+  </mergeCells>
+  <phoneticPr fontId="42" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Contents!A1" display="Back to contents" xr:uid="{F640A598-9E5A-4835-9386-045783020007}"/>
+  </hyperlinks>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="82" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3957F9A-7C4D-409C-A28F-BE8B87961F74}">
+  <sheetPr codeName="Sheet14">
+    <tabColor theme="6"/>
+  </sheetPr>
+  <dimension ref="A1:Y50"/>
+  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="11.7265625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" style="17" customWidth="1"/>
+    <col min="3" max="9" width="10" style="17" customWidth="1"/>
+    <col min="10" max="16384" width="9.453125" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="526"/>
+    </row>
+    <row r="2" spans="1:25" ht="18" customHeight="1" thickBot="1">
+      <c r="A2" s="15"/>
+      <c r="B2" s="964" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="965"/>
+      <c r="D2" s="965"/>
+      <c r="E2" s="965"/>
+      <c r="F2" s="965"/>
+      <c r="G2" s="965"/>
+      <c r="H2" s="965"/>
+      <c r="I2" s="966"/>
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" spans="1:25" ht="12.75" customHeight="1">
+      <c r="A3" s="15"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="105" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="909" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="909"/>
+      <c r="F3" s="909"/>
+      <c r="G3" s="909"/>
+      <c r="H3" s="909"/>
+      <c r="I3" s="910"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="559"/>
+      <c r="M3" s="559"/>
+      <c r="N3" s="559"/>
+      <c r="O3" s="559"/>
+      <c r="P3" s="559"/>
+      <c r="Q3" s="559"/>
+      <c r="S3" s="538"/>
+    </row>
+    <row r="4" spans="1:25" ht="12.75" customHeight="1">
+      <c r="A4" s="15"/>
+      <c r="B4" s="151"/>
+      <c r="C4" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="J4" s="15"/>
+      <c r="K4" s="532"/>
+      <c r="L4" s="532"/>
+      <c r="M4" s="532"/>
+      <c r="N4" s="532"/>
+      <c r="O4" s="532"/>
+      <c r="P4" s="532"/>
+      <c r="Q4" s="532"/>
+    </row>
+    <row r="5" spans="1:25" ht="13.5" customHeight="1">
+      <c r="A5" s="15"/>
+      <c r="B5" s="310" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="152">
+        <v>2108.7303043893562</v>
+      </c>
+      <c r="D5" s="152">
+        <v>2069.8474469367434</v>
+      </c>
+      <c r="E5" s="152">
+        <v>2027.3458030333193</v>
+      </c>
+      <c r="F5" s="152">
+        <v>2012.6406194934405</v>
+      </c>
+      <c r="G5" s="152">
+        <v>2001.8700847628832</v>
+      </c>
+      <c r="H5" s="152">
+        <v>1982.9201100206114</v>
+      </c>
+      <c r="I5" s="153">
+        <v>1962.5485885566063</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="763"/>
+      <c r="L5" s="763"/>
+      <c r="M5" s="763"/>
+      <c r="N5" s="763"/>
+      <c r="O5" s="763"/>
+      <c r="P5" s="763"/>
+      <c r="Q5" s="763"/>
+      <c r="S5" s="763"/>
+      <c r="T5" s="763"/>
+      <c r="U5" s="763"/>
+      <c r="V5" s="763"/>
+      <c r="W5" s="763"/>
+      <c r="X5" s="763"/>
+      <c r="Y5" s="763"/>
+    </row>
+    <row r="6" spans="1:25" ht="13.5" customHeight="1">
+      <c r="A6" s="15"/>
+      <c r="B6" s="310" t="s">
+        <v>208</v>
+      </c>
+      <c r="C6" s="152">
+        <v>1569.041217813324</v>
+      </c>
+      <c r="D6" s="152">
+        <v>1567.7826624097067</v>
+      </c>
+      <c r="E6" s="152">
+        <v>1540.2033043369458</v>
+      </c>
+      <c r="F6" s="152">
+        <v>1530.2485351419407</v>
+      </c>
+      <c r="G6" s="152">
+        <v>1520.7475110216285</v>
+      </c>
+      <c r="H6" s="152">
+        <v>1505.5439058920508</v>
+      </c>
+      <c r="I6" s="153">
+        <v>1491.4031570887553</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="763"/>
+      <c r="L6" s="763"/>
+      <c r="M6" s="763"/>
+      <c r="N6" s="763"/>
+      <c r="O6" s="763"/>
+      <c r="P6" s="763"/>
+      <c r="Q6" s="763"/>
+      <c r="S6" s="763"/>
+      <c r="T6" s="763"/>
+      <c r="U6" s="763"/>
+      <c r="V6" s="763"/>
+      <c r="W6" s="763"/>
+      <c r="X6" s="763"/>
+      <c r="Y6" s="763"/>
+    </row>
+    <row r="7" spans="1:25" ht="13.5" customHeight="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="204" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="154">
+        <v>1272.4562775587838</v>
+      </c>
+      <c r="D7" s="154">
+        <v>1262.3692523269856</v>
+      </c>
+      <c r="E7" s="154">
+        <v>1241.1318815407608</v>
+      </c>
+      <c r="F7" s="154">
+        <v>1235.8250379612948</v>
+      </c>
+      <c r="G7" s="154">
+        <v>1230.5012764962146</v>
+      </c>
+      <c r="H7" s="154">
+        <v>1218.4826638265554</v>
+      </c>
+      <c r="I7" s="155">
+        <v>1209.5688671337984</v>
+      </c>
+      <c r="J7" s="15"/>
+      <c r="K7" s="763"/>
+      <c r="L7" s="763"/>
+      <c r="M7" s="763"/>
+      <c r="N7" s="763"/>
+      <c r="O7" s="763"/>
+      <c r="P7" s="763"/>
+      <c r="Q7" s="763"/>
+      <c r="S7" s="763"/>
+      <c r="T7" s="763"/>
+      <c r="U7" s="763"/>
+      <c r="V7" s="763"/>
+      <c r="W7" s="763"/>
+      <c r="X7" s="763"/>
+      <c r="Y7" s="763"/>
+    </row>
+    <row r="8" spans="1:25" ht="12" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="958" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="967"/>
+      <c r="D8" s="967"/>
+      <c r="E8" s="967"/>
+      <c r="F8" s="967"/>
+      <c r="G8" s="967"/>
+      <c r="H8" s="967"/>
+      <c r="I8" s="968"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="763"/>
+      <c r="L8" s="763"/>
+      <c r="M8" s="763"/>
+      <c r="N8" s="763"/>
+      <c r="O8" s="763"/>
+      <c r="P8" s="763"/>
+      <c r="Q8" s="763"/>
+    </row>
+    <row r="9" spans="1:25" ht="12" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="954" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="955"/>
+      <c r="D9" s="955"/>
+      <c r="E9" s="955"/>
+      <c r="F9" s="955"/>
+      <c r="G9" s="955"/>
+      <c r="H9" s="955"/>
+      <c r="I9" s="956"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="763"/>
+      <c r="L9" s="763"/>
+      <c r="M9" s="763"/>
+      <c r="N9" s="763"/>
+      <c r="O9" s="763"/>
+      <c r="P9" s="763"/>
+      <c r="Q9" s="763"/>
+    </row>
+    <row r="10" spans="1:25" ht="12" customHeight="1" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="961" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="962"/>
+      <c r="D10" s="962"/>
+      <c r="E10" s="962"/>
+      <c r="F10" s="962"/>
+      <c r="G10" s="962"/>
+      <c r="H10" s="962"/>
+      <c r="I10" s="963"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="763"/>
+      <c r="L10" s="763"/>
+      <c r="M10" s="763"/>
+      <c r="N10" s="763"/>
+      <c r="O10" s="763"/>
+      <c r="P10" s="763"/>
+      <c r="Q10" s="763"/>
+    </row>
+    <row r="11" spans="1:25" ht="13.5" thickBot="1">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="763"/>
+      <c r="L11" s="763"/>
+      <c r="M11" s="763"/>
+      <c r="N11" s="763"/>
+      <c r="O11" s="763"/>
+      <c r="P11" s="763"/>
+      <c r="Q11" s="763"/>
+    </row>
+    <row r="12" spans="1:25" ht="18" customHeight="1" thickBot="1">
+      <c r="A12" s="15"/>
+      <c r="B12" s="964" t="s">
+        <v>308</v>
+      </c>
+      <c r="C12" s="965"/>
+      <c r="D12" s="965"/>
+      <c r="E12" s="965"/>
+      <c r="F12" s="965"/>
+      <c r="G12" s="965"/>
+      <c r="H12" s="965"/>
+      <c r="I12" s="966"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="763"/>
+      <c r="L12" s="763"/>
+      <c r="M12" s="763"/>
+      <c r="N12" s="763"/>
+      <c r="O12" s="763"/>
+      <c r="P12" s="763"/>
+      <c r="Q12" s="763"/>
+    </row>
+    <row r="13" spans="1:25" ht="12.75" customHeight="1">
+      <c r="A13" s="15"/>
+      <c r="B13" s="156"/>
+      <c r="C13" s="969" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="969"/>
+      <c r="E13" s="969"/>
+      <c r="F13" s="969"/>
+      <c r="G13" s="969"/>
+      <c r="H13" s="969"/>
+      <c r="I13" s="970"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="763"/>
+      <c r="L13" s="763"/>
+      <c r="M13" s="763"/>
+      <c r="N13" s="763"/>
+      <c r="O13" s="763"/>
+      <c r="P13" s="763"/>
+      <c r="Q13" s="763"/>
+    </row>
+    <row r="14" spans="1:25" ht="12.75" customHeight="1">
+      <c r="A14" s="15"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="105" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="971" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="971"/>
+      <c r="F14" s="971"/>
+      <c r="G14" s="971"/>
+      <c r="H14" s="971"/>
+      <c r="I14" s="972"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="763"/>
+      <c r="L14" s="763"/>
+      <c r="M14" s="763"/>
+      <c r="N14" s="763"/>
+      <c r="O14" s="763"/>
+      <c r="P14" s="763"/>
+      <c r="Q14" s="763"/>
+    </row>
+    <row r="15" spans="1:25" ht="12.75" customHeight="1">
+      <c r="A15" s="15"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="I15" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="J15" s="15"/>
+      <c r="K15" s="763"/>
+      <c r="L15" s="763"/>
+      <c r="M15" s="763"/>
+      <c r="N15" s="763"/>
+      <c r="O15" s="763"/>
+      <c r="P15" s="763"/>
+      <c r="Q15" s="763"/>
+    </row>
+    <row r="16" spans="1:25" ht="13.5" customHeight="1">
+      <c r="A16" s="15"/>
+      <c r="B16" s="310" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="157">
+        <v>3.7210000000000001</v>
+      </c>
+      <c r="D16" s="157">
+        <v>3.8017132735674961</v>
+      </c>
+      <c r="E16" s="157">
+        <v>3.8576304768846086</v>
+      </c>
+      <c r="F16" s="157">
+        <v>3.9611468028757213</v>
+      </c>
+      <c r="G16" s="157">
+        <v>4.0606048155270793</v>
+      </c>
+      <c r="H16" s="157">
+        <v>4.1207806264989637</v>
+      </c>
+      <c r="I16" s="158">
+        <v>4.1682755540802789</v>
+      </c>
+      <c r="J16" s="15"/>
+      <c r="K16" s="763"/>
+      <c r="L16" s="763"/>
+      <c r="M16" s="763"/>
+      <c r="N16" s="763"/>
+      <c r="O16" s="763"/>
+      <c r="P16" s="763"/>
+      <c r="Q16" s="763"/>
+      <c r="S16" s="763"/>
+      <c r="T16" s="763"/>
+      <c r="U16" s="763"/>
+      <c r="V16" s="763"/>
+      <c r="W16" s="763"/>
+      <c r="X16" s="763"/>
+      <c r="Y16" s="763"/>
+    </row>
+    <row r="17" spans="1:25" ht="13.5" customHeight="1">
+      <c r="A17" s="15"/>
+      <c r="B17" s="310" t="s">
+        <v>208</v>
+      </c>
+      <c r="C17" s="157">
+        <v>4.6340000000000003</v>
+      </c>
+      <c r="D17" s="157">
+        <v>4.7460251738734884</v>
+      </c>
+      <c r="E17" s="157">
+        <v>4.8714093827251164</v>
+      </c>
+      <c r="F17" s="157">
+        <v>4.9874652307456966</v>
+      </c>
+      <c r="G17" s="157">
+        <v>5.0956324197440548</v>
+      </c>
+      <c r="H17" s="157">
+        <v>5.1600022604647666</v>
+      </c>
+      <c r="I17" s="158">
+        <v>5.2213273828899034</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="763"/>
+      <c r="L17" s="763"/>
+      <c r="M17" s="763"/>
+      <c r="N17" s="763"/>
+      <c r="O17" s="763"/>
+      <c r="P17" s="763"/>
+      <c r="Q17" s="763"/>
+      <c r="S17" s="763"/>
+      <c r="T17" s="763"/>
+      <c r="U17" s="763"/>
+      <c r="V17" s="763"/>
+      <c r="W17" s="763"/>
+      <c r="X17" s="763"/>
+      <c r="Y17" s="763"/>
+    </row>
+    <row r="18" spans="1:25" ht="13.5" customHeight="1">
+      <c r="A18" s="15"/>
+      <c r="B18" s="310" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" s="157">
+        <v>4.077</v>
+      </c>
+      <c r="D18" s="157">
+        <v>4.2152050569449333</v>
+      </c>
+      <c r="E18" s="157">
+        <v>4.3266224223594447</v>
+      </c>
+      <c r="F18" s="157">
+        <v>4.4414458273607895</v>
+      </c>
+      <c r="G18" s="157">
+        <v>4.5475592478331839</v>
+      </c>
+      <c r="H18" s="157">
+        <v>4.6079582252695248</v>
+      </c>
+      <c r="I18" s="159">
+        <v>4.673773693595531</v>
+      </c>
+      <c r="J18" s="15"/>
+      <c r="K18" s="763"/>
+      <c r="L18" s="763"/>
+      <c r="M18" s="763"/>
+      <c r="N18" s="763"/>
+      <c r="O18" s="763"/>
+      <c r="P18" s="763"/>
+      <c r="Q18" s="763"/>
+      <c r="S18" s="763"/>
+      <c r="T18" s="763"/>
+      <c r="U18" s="763"/>
+      <c r="V18" s="763"/>
+      <c r="W18" s="763"/>
+      <c r="X18" s="763"/>
+      <c r="Y18" s="763"/>
+    </row>
+    <row r="19" spans="1:25" ht="12" customHeight="1">
+      <c r="A19" s="15"/>
+      <c r="B19" s="958" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="959"/>
+      <c r="D19" s="959"/>
+      <c r="E19" s="959"/>
+      <c r="F19" s="959"/>
+      <c r="G19" s="959"/>
+      <c r="H19" s="959"/>
+      <c r="I19" s="960"/>
+      <c r="J19" s="15"/>
+    </row>
+    <row r="20" spans="1:25" ht="12" customHeight="1">
+      <c r="A20" s="15"/>
+      <c r="B20" s="954" t="s">
+        <v>218</v>
+      </c>
+      <c r="C20" s="955"/>
+      <c r="D20" s="955"/>
+      <c r="E20" s="955"/>
+      <c r="F20" s="955"/>
+      <c r="G20" s="955"/>
+      <c r="H20" s="955"/>
+      <c r="I20" s="956"/>
+      <c r="J20" s="15"/>
+    </row>
+    <row r="21" spans="1:25" ht="12" customHeight="1" thickBot="1">
+      <c r="A21" s="15"/>
+      <c r="B21" s="961" t="s">
+        <v>217</v>
+      </c>
+      <c r="C21" s="962"/>
+      <c r="D21" s="962"/>
+      <c r="E21" s="962"/>
+      <c r="F21" s="962"/>
+      <c r="G21" s="962"/>
+      <c r="H21" s="962"/>
+      <c r="I21" s="963"/>
+      <c r="J21" s="15"/>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="B23" s="536"/>
+    </row>
+    <row r="24" spans="1:25" ht="18" customHeight="1">
+      <c r="B24" s="951"/>
+      <c r="C24" s="951"/>
+      <c r="D24" s="951"/>
+      <c r="E24" s="951"/>
+      <c r="F24" s="951"/>
+      <c r="G24" s="951"/>
+      <c r="H24" s="951"/>
+      <c r="I24" s="951"/>
+    </row>
+    <row r="25" spans="1:25" ht="12.75" customHeight="1">
+      <c r="B25" s="766"/>
+      <c r="C25" s="562"/>
+      <c r="D25" s="864"/>
+      <c r="E25" s="864"/>
+      <c r="F25" s="864"/>
+      <c r="G25" s="864"/>
+      <c r="H25" s="864"/>
+      <c r="I25" s="864"/>
+    </row>
+    <row r="26" spans="1:25" ht="12.75" customHeight="1">
+      <c r="B26" s="767"/>
+      <c r="C26" s="532"/>
+      <c r="D26" s="532"/>
+      <c r="E26" s="532"/>
+      <c r="F26" s="532"/>
+      <c r="G26" s="532"/>
+      <c r="H26" s="532"/>
+      <c r="I26" s="532"/>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="B27" s="524"/>
+      <c r="C27" s="152"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="152"/>
+      <c r="G27" s="152"/>
+      <c r="H27" s="152"/>
+      <c r="I27" s="152"/>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="B28" s="524"/>
+      <c r="C28" s="152"/>
+      <c r="D28" s="152"/>
+      <c r="E28" s="152"/>
+      <c r="F28" s="152"/>
+      <c r="G28" s="152"/>
+      <c r="H28" s="152"/>
+      <c r="I28" s="152"/>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="B29" s="524"/>
+      <c r="C29" s="152"/>
+      <c r="D29" s="152"/>
+      <c r="E29" s="152"/>
+      <c r="F29" s="152"/>
+      <c r="G29" s="152"/>
+      <c r="H29" s="152"/>
+      <c r="I29" s="152"/>
+    </row>
+    <row r="30" spans="1:25" ht="12" customHeight="1">
+      <c r="B30" s="953"/>
+      <c r="C30" s="957"/>
+      <c r="D30" s="957"/>
+      <c r="E30" s="957"/>
+      <c r="F30" s="957"/>
+      <c r="G30" s="957"/>
+      <c r="H30" s="957"/>
+      <c r="I30" s="957"/>
+    </row>
+    <row r="31" spans="1:25" ht="12" customHeight="1">
+      <c r="B31" s="957"/>
+      <c r="C31" s="957"/>
+      <c r="D31" s="957"/>
+      <c r="E31" s="957"/>
+      <c r="F31" s="957"/>
+      <c r="G31" s="957"/>
+      <c r="H31" s="957"/>
+      <c r="I31" s="957"/>
+    </row>
+    <row r="32" spans="1:25" ht="12" customHeight="1">
+      <c r="B32" s="953"/>
+      <c r="C32" s="953"/>
+      <c r="D32" s="953"/>
+      <c r="E32" s="953"/>
+      <c r="F32" s="953"/>
+      <c r="G32" s="953"/>
+      <c r="H32" s="953"/>
+      <c r="I32" s="953"/>
+    </row>
+    <row r="34" spans="2:9" ht="18.649999999999999" customHeight="1">
+      <c r="B34" s="951"/>
+      <c r="C34" s="951"/>
+      <c r="D34" s="951"/>
+      <c r="E34" s="951"/>
+      <c r="F34" s="951"/>
+      <c r="G34" s="951"/>
+      <c r="H34" s="951"/>
+      <c r="I34" s="951"/>
+    </row>
+    <row r="35" spans="2:9" ht="19.399999999999999" customHeight="1">
+      <c r="B35" s="632"/>
+      <c r="C35" s="973"/>
+      <c r="D35" s="973"/>
+      <c r="E35" s="973"/>
+      <c r="F35" s="973"/>
+      <c r="G35" s="973"/>
+      <c r="H35" s="973"/>
+      <c r="I35" s="973"/>
+    </row>
+    <row r="36" spans="2:9" ht="15.5">
+      <c r="B36" s="766"/>
+      <c r="C36" s="531"/>
+      <c r="D36" s="864"/>
+      <c r="E36" s="864"/>
+      <c r="F36" s="864"/>
+      <c r="G36" s="864"/>
+      <c r="H36" s="864"/>
+      <c r="I36" s="864"/>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37" s="767"/>
+      <c r="C37" s="532"/>
+      <c r="D37" s="532"/>
+      <c r="E37" s="532"/>
+      <c r="F37" s="532"/>
+      <c r="G37" s="532"/>
+      <c r="H37" s="532"/>
+      <c r="I37" s="532"/>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38" s="524"/>
+      <c r="C38" s="768"/>
+      <c r="D38" s="768"/>
+      <c r="E38" s="768"/>
+      <c r="F38" s="768"/>
+      <c r="G38" s="768"/>
+      <c r="H38" s="768"/>
+      <c r="I38" s="768"/>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39" s="524"/>
+      <c r="C39" s="768"/>
+      <c r="D39" s="768"/>
+      <c r="E39" s="768"/>
+      <c r="F39" s="768"/>
+      <c r="G39" s="768"/>
+      <c r="H39" s="768"/>
+      <c r="I39" s="768"/>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" s="524"/>
+      <c r="C40" s="768"/>
+      <c r="D40" s="768"/>
+      <c r="E40" s="768"/>
+      <c r="F40" s="768"/>
+      <c r="G40" s="768"/>
+      <c r="H40" s="768"/>
+      <c r="I40" s="768"/>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41" s="764"/>
+      <c r="C41" s="769"/>
+      <c r="D41" s="769"/>
+      <c r="E41" s="769"/>
+      <c r="F41" s="769"/>
+      <c r="G41" s="769"/>
+      <c r="H41" s="769"/>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43" s="536"/>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="C44" s="770"/>
+      <c r="D44" s="770"/>
+      <c r="E44" s="770"/>
+      <c r="F44" s="770"/>
+      <c r="G44" s="770"/>
+      <c r="H44" s="770"/>
+      <c r="I44" s="770"/>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="538"/>
+      <c r="C46" s="771"/>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="536"/>
+      <c r="C48" s="765"/>
+      <c r="D48" s="765"/>
+      <c r="E48" s="765"/>
+      <c r="F48" s="765"/>
+      <c r="G48" s="765"/>
+      <c r="H48" s="765"/>
+      <c r="I48" s="765"/>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" s="536"/>
+      <c r="C49" s="765"/>
+      <c r="D49" s="765"/>
+      <c r="E49" s="765"/>
+      <c r="F49" s="765"/>
+      <c r="G49" s="765"/>
+      <c r="H49" s="765"/>
+      <c r="I49" s="765"/>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" s="536"/>
+      <c r="C50" s="765"/>
+      <c r="D50" s="765"/>
+      <c r="E50" s="765"/>
+      <c r="F50" s="765"/>
+      <c r="G50" s="765"/>
+      <c r="H50" s="765"/>
+      <c r="I50" s="765"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="D36:I36"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B21:I21"/>
+  </mergeCells>
+  <phoneticPr fontId="42" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Contents!A1" display="Back to contents" xr:uid="{9FA62B33-BAC6-4FD9-A12D-4178AF2CE126}"/>
+  </hyperlinks>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="82" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C832A33-B09A-486C-90AD-7C64006FA8C9}">
   <sheetPr codeName="Sheet25">
